--- a/master/result/64_职场恋曲_霸总的温柔教师/64_职场恋曲_霸总的温柔教师.xlsx
+++ b/master/result/64_职场恋曲_霸总的温柔教师/64_职场恋曲_霸总的温柔教师.xlsx
@@ -397,577 +397,731 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:D51"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文含义</v>
+        <v>词性</v>
+      </c>
+      <c r="D1" t="str">
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>today</v>
       </c>
       <c r="B2" t="str">
-        <v>today</v>
+        <v>/today/</v>
       </c>
       <c r="C2" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>今天</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>east</v>
       </c>
       <c r="B3" t="str">
-        <v>east</v>
+        <v>/east/</v>
       </c>
       <c r="C3" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>东方</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>teacher</v>
       </c>
       <c r="B4" t="str">
-        <v>teacher</v>
+        <v>/teacher/</v>
       </c>
       <c r="C4" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D4" t="str">
         <v>教师</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>hospitality</v>
       </c>
       <c r="B5" t="str">
-        <v>hospitality</v>
+        <v>/hospitality/</v>
       </c>
       <c r="C5" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D5" t="str">
         <v>好客</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>employer</v>
       </c>
       <c r="B6" t="str">
-        <v>employer</v>
+        <v>/employer/</v>
       </c>
       <c r="C6" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D6" t="str">
         <v>雇主</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>pen</v>
       </c>
       <c r="B7" t="str">
-        <v>pen</v>
+        <v>/pen/</v>
       </c>
       <c r="C7" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D7" t="str">
         <v>钢笔</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>some</v>
       </c>
       <c r="B8" t="str">
-        <v>some</v>
+        <v>/some/</v>
       </c>
       <c r="C8" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D8" t="str">
         <v>一些</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>must</v>
       </c>
       <c r="B9" t="str">
-        <v>must</v>
+        <v>/must/</v>
       </c>
       <c r="C9" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D9" t="str">
         <v>必须</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>understanding</v>
       </c>
       <c r="B10" t="str">
-        <v>understanding</v>
+        <v>/understanding/</v>
       </c>
       <c r="C10" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D10" t="str">
         <v>理解</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>beside</v>
       </c>
       <c r="B11" t="str">
-        <v>beside</v>
+        <v>/beside/</v>
       </c>
       <c r="C11" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D11" t="str">
         <v>在旁边</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>little</v>
       </c>
       <c r="B12" t="str">
-        <v>little</v>
+        <v>/little/</v>
       </c>
       <c r="C12" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D12" t="str">
         <v>小的</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>wet</v>
       </c>
       <c r="B13" t="str">
-        <v>wet</v>
+        <v>/wet/</v>
       </c>
       <c r="C13" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D13" t="str">
         <v>湿的</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>successive</v>
       </c>
       <c r="B14" t="str">
-        <v>successive</v>
+        <v>/successive/</v>
       </c>
       <c r="C14" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D14" t="str">
         <v>连续的</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>accent</v>
       </c>
       <c r="B15" t="str">
-        <v>accent</v>
+        <v>/accent/</v>
       </c>
       <c r="C15" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D15" t="str">
         <v>口音</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>flush</v>
       </c>
       <c r="B16" t="str">
-        <v>flush</v>
+        <v>/flush/</v>
       </c>
       <c r="C16" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D16" t="str">
         <v>脸红</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>prominent</v>
       </c>
       <c r="B17" t="str">
-        <v>prominent</v>
+        <v>/prominent/</v>
       </c>
       <c r="C17" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D17" t="str">
         <v>杰出的</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>prevalent</v>
       </c>
       <c r="B18" t="str">
-        <v>prevalent</v>
+        <v>/prevalent/</v>
       </c>
       <c r="C18" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D18" t="str">
         <v>流行的</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>thermometer</v>
       </c>
       <c r="B19" t="str">
-        <v>thermometer</v>
+        <v>/thermometer/</v>
       </c>
       <c r="C19" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D19" t="str">
         <v>温度计</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>matter</v>
       </c>
       <c r="B20" t="str">
-        <v>matter</v>
+        <v>/ˈmætə/</v>
       </c>
       <c r="C20" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D20" t="str">
         <v>物质</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>spiritual</v>
       </c>
       <c r="B21" t="str">
-        <v>spiritual</v>
+        <v>/spiritual/</v>
       </c>
       <c r="C21" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D21" t="str">
         <v>精神的</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>allocate</v>
       </c>
       <c r="B22" t="str">
-        <v>allocate</v>
+        <v>/allocate/</v>
       </c>
       <c r="C22" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D22" t="str">
         <v>分配</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>homogeneous</v>
       </c>
       <c r="B23" t="str">
-        <v>homogeneous</v>
+        <v>/homogeneous/</v>
       </c>
       <c r="C23" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D23" t="str">
         <v>同类的</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>criticism</v>
       </c>
       <c r="B24" t="str">
-        <v>criticism</v>
+        <v>/ˈkrɪtɪsɪzəm/</v>
       </c>
       <c r="C24" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D24" t="str">
         <v>批评</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>legal</v>
       </c>
       <c r="B25" t="str">
-        <v>legal</v>
+        <v>/legal/</v>
       </c>
       <c r="C25" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D25" t="str">
         <v>合法的</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>benign</v>
       </c>
       <c r="B26" t="str">
-        <v>benign</v>
+        <v>/benign/</v>
       </c>
       <c r="C26" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D26" t="str">
         <v>仁慈的</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>whistle</v>
       </c>
       <c r="B27" t="str">
-        <v>whistle</v>
+        <v>/whistle/</v>
       </c>
       <c r="C27" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D27" t="str">
         <v>口哨</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>retain</v>
       </c>
       <c r="B28" t="str">
-        <v>retain</v>
+        <v>/rɪˈteɪn/</v>
       </c>
       <c r="C28" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D28" t="str">
         <v>保留</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>chess</v>
       </c>
       <c r="B29" t="str">
-        <v>chess</v>
+        <v>/tʃes/</v>
       </c>
       <c r="C29" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D29" t="str">
         <v>国际象棋</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>consent</v>
       </c>
       <c r="B30" t="str">
-        <v>consent</v>
+        <v>/consent/</v>
       </c>
       <c r="C30" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D30" t="str">
         <v>同意</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>testimony</v>
       </c>
       <c r="B31" t="str">
-        <v>testimony</v>
+        <v>/testimony/</v>
       </c>
       <c r="C31" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D31" t="str">
         <v>证据</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>indignation</v>
       </c>
       <c r="B32" t="str">
-        <v>indignation</v>
+        <v>/indignation/</v>
       </c>
       <c r="C32" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D32" t="str">
         <v>愤怒</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>guarantee</v>
       </c>
       <c r="B33" t="str">
-        <v>guarantee</v>
+        <v>/ˌɡærənˈtiː/</v>
       </c>
       <c r="C33" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D33" t="str">
         <v>保证</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>autonomy</v>
       </c>
       <c r="B34" t="str">
-        <v>autonomy</v>
+        <v>/autonomy/</v>
       </c>
       <c r="C34" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D34" t="str">
         <v>自治</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>telephone</v>
       </c>
       <c r="B35" t="str">
-        <v>telephone</v>
+        <v>/telephone/</v>
       </c>
       <c r="C35" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D35" t="str">
         <v>电话</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>out</v>
       </c>
       <c r="B36" t="str">
-        <v>out</v>
+        <v>/out/</v>
       </c>
       <c r="C36" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D36" t="str">
         <v>出去</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>bankrupt</v>
       </c>
       <c r="B37" t="str">
-        <v>bankrupt</v>
+        <v>/bankrupt/</v>
       </c>
       <c r="C37" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D37" t="str">
         <v>破产</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>manufacture</v>
       </c>
       <c r="B38" t="str">
-        <v>manufacture</v>
+        <v>/manufacture/</v>
       </c>
       <c r="C38" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D38" t="str">
         <v>制造</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>ballot</v>
       </c>
       <c r="B39" t="str">
-        <v>ballot</v>
+        <v>/ballot/</v>
       </c>
       <c r="C39" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D39" t="str">
         <v>投票</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>transfer</v>
       </c>
       <c r="B40" t="str">
-        <v>transfer</v>
+        <v>/trænsˈfɜː/</v>
       </c>
       <c r="C40" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D40" t="str">
         <v>转移</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>shade</v>
       </c>
       <c r="B41" t="str">
-        <v>shade</v>
+        <v>/shade/</v>
       </c>
       <c r="C41" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D41" t="str">
         <v>阴影</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>withdraw</v>
       </c>
       <c r="B42" t="str">
-        <v>withdraw</v>
+        <v>/wɪðˈdrɔː/</v>
       </c>
       <c r="C42" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D42" t="str">
         <v>撤回</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>raw</v>
       </c>
       <c r="B43" t="str">
-        <v>raw</v>
+        <v>/raw/</v>
       </c>
       <c r="C43" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D43" t="str">
         <v>生的</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>who</v>
       </c>
       <c r="B44" t="str">
-        <v>who</v>
+        <v>/who/</v>
       </c>
       <c r="C44" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D44" t="str">
         <v>谁</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>nightmare</v>
       </c>
       <c r="B45" t="str">
-        <v>nightmare</v>
+        <v>/nightmare/</v>
       </c>
       <c r="C45" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D45" t="str">
         <v>噩梦</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>withstand</v>
       </c>
       <c r="B46" t="str">
-        <v>withstand</v>
+        <v>/withstand/</v>
       </c>
       <c r="C46" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D46" t="str">
         <v>抵抗</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>reel</v>
       </c>
       <c r="B47" t="str">
-        <v>reel</v>
+        <v>/reel/</v>
       </c>
       <c r="C47" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D47" t="str">
         <v>卷筒</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>loose</v>
       </c>
       <c r="B48" t="str">
-        <v>loose</v>
+        <v>/loose/</v>
       </c>
       <c r="C48" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D48" t="str">
         <v>松的</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>inward</v>
       </c>
       <c r="B49" t="str">
-        <v>inward</v>
+        <v>/inward/</v>
       </c>
       <c r="C49" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D49" t="str">
         <v>向内的</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
+      <c r="A50" t="str">
+        <v>submerge</v>
       </c>
       <c r="B50" t="str">
-        <v>submerge</v>
+        <v>/submerge/</v>
       </c>
       <c r="C50" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D50" t="str">
         <v>淹没</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51">
-        <v>50</v>
+      <c r="A51" t="str">
+        <v>fetch</v>
       </c>
       <c r="B51" t="str">
-        <v>fetch</v>
+        <v>/fetʃ/</v>
       </c>
       <c r="C51" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D51" t="str">
         <v>取来</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D51"/>
   </ignoredErrors>
 </worksheet>
 </file>